--- a/China NEA/raw_tables_xlsx/2024-05-06_2024年一季度光伏发电建设情况---国家能源局_raw.xlsx
+++ b/China NEA/raw_tables_xlsx/2024-05-06_2024年一季度光伏发电建设情况---国家能源局_raw.xlsx
@@ -14,33 +14,810 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="268">
   <si>
     <t>总计</t>
   </si>
   <si>
-    <t>457</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>北京</t>
+  </si>
+  <si>
+    <t>天津</t>
+  </si>
+  <si>
+    <t>河北</t>
+  </si>
+  <si>
+    <t>山西</t>
+  </si>
+  <si>
+    <t>山东</t>
+  </si>
+  <si>
+    <t>内蒙古</t>
+  </si>
+  <si>
+    <t>辽宁</t>
+  </si>
+  <si>
+    <t>吉林</t>
+  </si>
+  <si>
+    <t>黑龙江</t>
+  </si>
+  <si>
+    <t>上海</t>
+  </si>
+  <si>
+    <t>江苏</t>
+  </si>
+  <si>
+    <t>浙江</t>
+  </si>
+  <si>
+    <t>安徽</t>
+  </si>
+  <si>
+    <t>福建</t>
+  </si>
+  <si>
+    <t>江西</t>
+  </si>
+  <si>
+    <t>河南</t>
+  </si>
+  <si>
+    <t>湖北</t>
+  </si>
+  <si>
+    <t>湖南</t>
+  </si>
+  <si>
+    <t>重庆</t>
+  </si>
+  <si>
+    <t>四川</t>
+  </si>
+  <si>
+    <t>陕西</t>
+  </si>
+  <si>
+    <t>甘肃</t>
+  </si>
+  <si>
+    <t>青海</t>
+  </si>
+  <si>
+    <t>宁夏</t>
+  </si>
+  <si>
+    <t>新疆</t>
+  </si>
+  <si>
+    <t>新疆兵团</t>
+  </si>
+  <si>
+    <t>西藏</t>
+  </si>
+  <si>
+    <t>广东</t>
+  </si>
+  <si>
+    <t>广西</t>
+  </si>
+  <si>
+    <t>海南</t>
+  </si>
+  <si>
+    <t>贵州</t>
+  </si>
+  <si>
+    <t>云南</t>
+  </si>
+  <si>
+    <t>4574</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>57.7</t>
+  </si>
+  <si>
+    <t>313.1</t>
+  </si>
+  <si>
+    <t>151.8</t>
+  </si>
+  <si>
+    <t>323.0</t>
+  </si>
+  <si>
+    <t>340.3</t>
+  </si>
+  <si>
+    <t>79.9</t>
+  </si>
+  <si>
+    <t>22.7</t>
+  </si>
+  <si>
+    <t>13.2</t>
+  </si>
+  <si>
+    <t>18.9</t>
+  </si>
+  <si>
+    <t>492.7</t>
+  </si>
+  <si>
+    <t>240.3</t>
+  </si>
+  <si>
+    <t>209.4</t>
+  </si>
+  <si>
+    <t>99.8</t>
+  </si>
+  <si>
+    <t>126.6</t>
+  </si>
+  <si>
+    <t>147.9</t>
+  </si>
+  <si>
+    <t>212.5</t>
+  </si>
+  <si>
+    <t>89.6</t>
+  </si>
+  <si>
+    <t>31.6</t>
+  </si>
+  <si>
+    <t>86.2</t>
+  </si>
+  <si>
+    <t>56.8</t>
+  </si>
+  <si>
+    <t>162.9</t>
+  </si>
+  <si>
+    <t>117.9</t>
+  </si>
+  <si>
+    <t>105.6</t>
+  </si>
+  <si>
+    <t>206.9</t>
+  </si>
+  <si>
+    <t>47.1</t>
+  </si>
+  <si>
+    <t>14.6</t>
+  </si>
+  <si>
+    <t>157.9</t>
+  </si>
+  <si>
+    <t>186.1</t>
+  </si>
+  <si>
+    <t>177.0</t>
+  </si>
+  <si>
+    <t>82.1</t>
+  </si>
+  <si>
+    <t>198.7</t>
+  </si>
+  <si>
+    <t>2193</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>10.1</t>
+  </si>
+  <si>
+    <t>204.0</t>
+  </si>
+  <si>
+    <t>103.5</t>
+  </si>
+  <si>
+    <t>75.3</t>
+  </si>
+  <si>
+    <t>310.0</t>
+  </si>
+  <si>
+    <t>10.6</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>47.8</t>
+  </si>
+  <si>
+    <t>19.1</t>
+  </si>
+  <si>
+    <t>30.6</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>71.4</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>84.1</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>11.7</t>
+  </si>
+  <si>
+    <t>80.6</t>
+  </si>
+  <si>
+    <t>6.8</t>
+  </si>
+  <si>
+    <t>148.5</t>
+  </si>
+  <si>
+    <t>117.0</t>
+  </si>
+  <si>
+    <t>98.3</t>
+  </si>
+  <si>
+    <t>206.5</t>
+  </si>
+  <si>
+    <t>33.6</t>
+  </si>
+  <si>
+    <t>37.8</t>
+  </si>
+  <si>
+    <t>159.1</t>
+  </si>
+  <si>
+    <t>79.6</t>
+  </si>
+  <si>
+    <t>163.5</t>
+  </si>
+  <si>
+    <t>2381</t>
+  </si>
+  <si>
+    <t>47.6</t>
+  </si>
+  <si>
+    <t>109.0</t>
+  </si>
+  <si>
+    <t>48.3</t>
+  </si>
+  <si>
+    <t>247.6</t>
+  </si>
+  <si>
+    <t>30.3</t>
+  </si>
+  <si>
+    <t>69.3</t>
+  </si>
+  <si>
+    <t>15.7</t>
+  </si>
+  <si>
+    <t>444.9</t>
+  </si>
+  <si>
+    <t>221.2</t>
+  </si>
+  <si>
+    <t>178.8</t>
+  </si>
+  <si>
+    <t>99.2</t>
+  </si>
+  <si>
+    <t>55.2</t>
+  </si>
+  <si>
+    <t>147.8</t>
+  </si>
+  <si>
+    <t>128.5</t>
+  </si>
+  <si>
+    <t>19.9</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>124.3</t>
+  </si>
+  <si>
+    <t>148.3</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>35.3</t>
+  </si>
+  <si>
+    <t>692</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>42.4</t>
+  </si>
+  <si>
+    <t>27.7</t>
+  </si>
+  <si>
+    <t>73.1</t>
+  </si>
+  <si>
+    <t>48.0</t>
+  </si>
+  <si>
+    <t>9.8</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>203.3</t>
+  </si>
+  <si>
+    <t>16.5</t>
+  </si>
+  <si>
+    <t>68.7</t>
+  </si>
+  <si>
+    <t>22.0</t>
+  </si>
+  <si>
+    <t>17.3</t>
+  </si>
+  <si>
+    <t>35.4</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>11.9</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>40.4</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>65950</t>
+  </si>
+  <si>
+    <t>111.1</t>
+  </si>
+  <si>
+    <t>547.1</t>
+  </si>
+  <si>
+    <t>5712.0</t>
+  </si>
+  <si>
+    <t>2642.3</t>
+  </si>
+  <si>
+    <t>6015.5</t>
+  </si>
+  <si>
+    <t>2681.8</t>
+  </si>
+  <si>
+    <t>1037.6</t>
+  </si>
+  <si>
+    <t>482.5</t>
+  </si>
+  <si>
+    <t>578.1</t>
+  </si>
+  <si>
+    <t>308.3</t>
+  </si>
+  <si>
+    <t>4420.8</t>
+  </si>
+  <si>
+    <t>3597.0</t>
+  </si>
+  <si>
+    <t>3432.5</t>
+  </si>
+  <si>
+    <t>974.3</t>
+  </si>
+  <si>
+    <t>2119.9</t>
+  </si>
+  <si>
+    <t>3879.2</t>
+  </si>
+  <si>
+    <t>2700.1</t>
+  </si>
+  <si>
+    <t>1341.4</t>
+  </si>
+  <si>
+    <t>188.4</t>
+  </si>
+  <si>
+    <t>659.8</t>
+  </si>
+  <si>
+    <t>2348.8</t>
+  </si>
+  <si>
+    <t>2681.7</t>
+  </si>
+  <si>
+    <t>2658.1</t>
+  </si>
+  <si>
+    <t>2242.1</t>
+  </si>
+  <si>
+    <t>3149.6</t>
+  </si>
+  <si>
+    <t>273.5</t>
+  </si>
+  <si>
+    <t>271.2</t>
+  </si>
+  <si>
+    <t>2926.4</t>
+  </si>
+  <si>
+    <t>1319.0</t>
+  </si>
+  <si>
+    <t>649.4</t>
+  </si>
+  <si>
+    <t>1729.8</t>
+  </si>
+  <si>
+    <t>2270.5</t>
+  </si>
+  <si>
+    <t>37950</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>309.1</t>
+  </si>
+  <si>
+    <t>3210.3</t>
+  </si>
+  <si>
+    <t>1927.6</t>
+  </si>
+  <si>
+    <t>1669.1</t>
+  </si>
+  <si>
+    <t>2471.6</t>
+  </si>
+  <si>
+    <t>531.9</t>
+  </si>
+  <si>
+    <t>347.1</t>
+  </si>
+  <si>
+    <t>396.1</t>
+  </si>
+  <si>
+    <t>39.8</t>
+  </si>
+  <si>
+    <t>1203.6</t>
+  </si>
+  <si>
+    <t>686.2</t>
+  </si>
+  <si>
+    <t>1316.6</t>
+  </si>
+  <si>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>1052.6</t>
+  </si>
+  <si>
+    <t>630.0</t>
+  </si>
+  <si>
+    <t>1840.2</t>
+  </si>
+  <si>
+    <t>413.6</t>
+  </si>
+  <si>
+    <t>96.7</t>
+  </si>
+  <si>
+    <t>603.4</t>
+  </si>
+  <si>
+    <t>1826.9</t>
+  </si>
+  <si>
+    <t>2563.3</t>
+  </si>
+  <si>
+    <t>2638.0</t>
+  </si>
+  <si>
+    <t>2109.8</t>
+  </si>
+  <si>
+    <t>3131.20</t>
+  </si>
+  <si>
+    <t>266.5</t>
+  </si>
+  <si>
+    <t>1224.5</t>
+  </si>
+  <si>
+    <t>854.5</t>
+  </si>
+  <si>
+    <t>468.9</t>
+  </si>
+  <si>
+    <t>1696.5</t>
+  </si>
+  <si>
+    <t>2101.3</t>
+  </si>
+  <si>
+    <t>28000</t>
+  </si>
+  <si>
+    <t>106.0</t>
+  </si>
+  <si>
+    <t>238.0</t>
+  </si>
+  <si>
+    <t>2501.6</t>
+  </si>
+  <si>
+    <t>714.7</t>
+  </si>
+  <si>
+    <t>4346.4</t>
+  </si>
+  <si>
+    <t>210.2</t>
+  </si>
+  <si>
+    <t>505.6</t>
+  </si>
+  <si>
+    <t>135.4</t>
+  </si>
+  <si>
+    <t>182.0</t>
+  </si>
+  <si>
+    <t>268.5</t>
+  </si>
+  <si>
+    <t>3217.1</t>
+  </si>
+  <si>
+    <t>2910.8</t>
+  </si>
+  <si>
+    <t>2115.9</t>
+  </si>
+  <si>
+    <t>929.6</t>
+  </si>
+  <si>
+    <t>1067.3</t>
+  </si>
+  <si>
+    <t>3249.3</t>
+  </si>
+  <si>
+    <t>859.9</t>
+  </si>
+  <si>
+    <t>927.8</t>
+  </si>
+  <si>
+    <t>91.7</t>
+  </si>
+  <si>
+    <t>56.4</t>
+  </si>
+  <si>
+    <t>521.9</t>
+  </si>
+  <si>
+    <t>118.4</t>
+  </si>
+  <si>
+    <t>20.1</t>
+  </si>
+  <si>
+    <t>132.3</t>
+  </si>
+  <si>
+    <t>18.4</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>1701.9</t>
+  </si>
+  <si>
+    <t>464.5</t>
+  </si>
+  <si>
+    <t>180.5</t>
+  </si>
+  <si>
+    <t>33.4</t>
+  </si>
+  <si>
+    <t>169.1</t>
+  </si>
+  <si>
+    <t>12294</t>
+  </si>
+  <si>
+    <t>38.3</t>
+  </si>
+  <si>
+    <t>1773.7</t>
+  </si>
+  <si>
+    <t>512.6</t>
+  </si>
+  <si>
+    <t>2629.0</t>
+  </si>
+  <si>
+    <t>68.3</t>
+  </si>
+  <si>
+    <t>266.0</t>
+  </si>
+  <si>
+    <t>52.3</t>
+  </si>
+  <si>
+    <t>43.9</t>
+  </si>
+  <si>
+    <t>21.5</t>
+  </si>
+  <si>
+    <t>1062.6</t>
+  </si>
+  <si>
+    <t>253.5</t>
+  </si>
+  <si>
+    <t>1035.5</t>
+  </si>
+  <si>
+    <t>362.1</t>
+  </si>
+  <si>
+    <t>590.2</t>
+  </si>
+  <si>
+    <t>2266.6</t>
+  </si>
+  <si>
+    <t>303.4</t>
+  </si>
+  <si>
+    <t>313.6</t>
+  </si>
+  <si>
+    <t>15.3</t>
+  </si>
+  <si>
+    <t>292.1</t>
+  </si>
+  <si>
+    <t>29.1</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>242.1</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>25.1</t>
   </si>
 </sst>
 </file>
@@ -372,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -380,28 +1157,956 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" t="s">
+        <v>212</v>
+      </c>
+      <c r="I5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" t="s">
+        <v>215</v>
+      </c>
+      <c r="I8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
         <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H10" t="s">
+        <v>217</v>
+      </c>
+      <c r="I10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" t="s">
+        <v>154</v>
+      </c>
+      <c r="G12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H12" t="s">
+        <v>219</v>
+      </c>
+      <c r="I12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" t="s">
+        <v>131</v>
+      </c>
+      <c r="F13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G13" t="s">
+        <v>188</v>
+      </c>
+      <c r="H13" t="s">
+        <v>220</v>
+      </c>
+      <c r="I13" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" t="s">
+        <v>156</v>
+      </c>
+      <c r="G14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H14" t="s">
+        <v>221</v>
+      </c>
+      <c r="I14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15" t="s">
+        <v>157</v>
+      </c>
+      <c r="G15" t="s">
+        <v>190</v>
+      </c>
+      <c r="H15" t="s">
+        <v>222</v>
+      </c>
+      <c r="I15" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" t="s">
+        <v>191</v>
+      </c>
+      <c r="H16" t="s">
+        <v>223</v>
+      </c>
+      <c r="I16" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17" t="s">
+        <v>159</v>
+      </c>
+      <c r="G17" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" t="s">
+        <v>224</v>
+      </c>
+      <c r="I17" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" t="s">
+        <v>136</v>
+      </c>
+      <c r="F18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G18" t="s">
+        <v>193</v>
+      </c>
+      <c r="H18" t="s">
+        <v>225</v>
+      </c>
+      <c r="I18" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" t="s">
+        <v>161</v>
+      </c>
+      <c r="G19" t="s">
+        <v>194</v>
+      </c>
+      <c r="H19" t="s">
+        <v>226</v>
+      </c>
+      <c r="I19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G20" t="s">
+        <v>195</v>
+      </c>
+      <c r="H20" t="s">
+        <v>227</v>
+      </c>
+      <c r="I20" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" t="s">
+        <v>163</v>
+      </c>
+      <c r="G21" t="s">
+        <v>196</v>
+      </c>
+      <c r="H21" t="s">
+        <v>228</v>
+      </c>
+      <c r="I21" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" t="s">
+        <v>197</v>
+      </c>
+      <c r="H22" t="s">
+        <v>229</v>
+      </c>
+      <c r="I22" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" t="s">
+        <v>165</v>
+      </c>
+      <c r="G23" t="s">
+        <v>198</v>
+      </c>
+      <c r="H23" t="s">
+        <v>230</v>
+      </c>
+      <c r="I23" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" t="s">
+        <v>199</v>
+      </c>
+      <c r="H24" t="s">
+        <v>231</v>
+      </c>
+      <c r="I24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25" t="s">
+        <v>232</v>
+      </c>
+      <c r="I25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" t="s">
+        <v>201</v>
+      </c>
+      <c r="H26" t="s">
+        <v>233</v>
+      </c>
+      <c r="I26" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" t="s">
+        <v>169</v>
+      </c>
+      <c r="G27" t="s">
+        <v>169</v>
+      </c>
+      <c r="H27" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" t="s">
+        <v>202</v>
+      </c>
+      <c r="H28" t="s">
+        <v>234</v>
+      </c>
+      <c r="I28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" t="s">
+        <v>171</v>
+      </c>
+      <c r="G29" t="s">
+        <v>203</v>
+      </c>
+      <c r="H29" t="s">
+        <v>235</v>
+      </c>
+      <c r="I29" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" t="s">
+        <v>138</v>
+      </c>
+      <c r="F30" t="s">
+        <v>172</v>
+      </c>
+      <c r="G30" t="s">
+        <v>204</v>
+      </c>
+      <c r="H30" t="s">
+        <v>236</v>
+      </c>
+      <c r="I30" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F31" t="s">
+        <v>173</v>
+      </c>
+      <c r="G31" t="s">
+        <v>205</v>
+      </c>
+      <c r="H31" t="s">
+        <v>237</v>
+      </c>
+      <c r="I31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" t="s">
+        <v>174</v>
+      </c>
+      <c r="G32" t="s">
+        <v>206</v>
+      </c>
+      <c r="H32" t="s">
+        <v>238</v>
+      </c>
+      <c r="I32" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" t="s">
+        <v>175</v>
+      </c>
+      <c r="G33" t="s">
+        <v>207</v>
+      </c>
+      <c r="H33" t="s">
+        <v>239</v>
+      </c>
+      <c r="I33" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
